--- a/artfynd/A 23748-2026 artfynd.xlsx
+++ b/artfynd/A 23748-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133885875</v>
+        <v>133885710</v>
       </c>
       <c r="B2" t="n">
         <v>57162</v>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592612</v>
+        <v>592579</v>
       </c>
       <c r="R2" t="n">
-        <v>6394302</v>
+        <v>6394274</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,6 +768,11 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färsk tjäderspillning i hällmarkskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +799,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133885710</v>
+        <v>133885875</v>
       </c>
       <c r="B3" t="n">
         <v>57162</v>
@@ -841,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592579</v>
+        <v>592612</v>
       </c>
       <c r="R3" t="n">
-        <v>6394274</v>
+        <v>6394302</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,11 +892,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färsk tjäderspillning i hällmarkskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
